--- a/pass.xlsx
+++ b/pass.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{426B7D7A-21C4-A048-98C8-D998A9D7C601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{86EEAD34-86B3-4466-AB6D-62E57924479D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{86EEAD34-86B3-4466-AB6D-62E57924479D}"/>
   </bookViews>
   <sheets>
     <sheet name="KP" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="86">
   <si>
     <t>Արարատ Արմեն</t>
   </si>
@@ -126,91 +126,91 @@
     <t>Հոմպլեքս Հիպեր Մոլ ՍՊԸ</t>
   </si>
   <si>
-    <t>006461</t>
-  </si>
-  <si>
-    <t>024161</t>
-  </si>
-  <si>
-    <t>020661</t>
-  </si>
-  <si>
-    <t>011961</t>
-  </si>
-  <si>
-    <t>018961</t>
-  </si>
-  <si>
-    <t>025361</t>
-  </si>
-  <si>
-    <t>000261</t>
-  </si>
-  <si>
-    <t>003661</t>
-  </si>
-  <si>
-    <t>005361</t>
-  </si>
-  <si>
-    <t>005861</t>
-  </si>
-  <si>
-    <t>008161</t>
-  </si>
-  <si>
-    <t>009761</t>
-  </si>
-  <si>
-    <t>009861</t>
-  </si>
-  <si>
-    <t>013561</t>
-  </si>
-  <si>
-    <t>014861</t>
-  </si>
-  <si>
-    <t>015861</t>
-  </si>
-  <si>
-    <t>018561</t>
-  </si>
-  <si>
-    <t>019361</t>
-  </si>
-  <si>
-    <t>019661</t>
-  </si>
-  <si>
-    <t>021261</t>
-  </si>
-  <si>
-    <t>022161</t>
-  </si>
-  <si>
-    <t>023161</t>
-  </si>
-  <si>
-    <t>023261</t>
-  </si>
-  <si>
-    <t>024261</t>
-  </si>
-  <si>
-    <t>024361</t>
-  </si>
-  <si>
-    <t>024561</t>
-  </si>
-  <si>
-    <t>025261</t>
-  </si>
-  <si>
-    <t>051061</t>
-  </si>
-  <si>
     <t>pass</t>
+  </si>
+  <si>
+    <t>7d147b1c41150dc0b4f335a5dec2e37eb876fc3f40106346ed4876de6b38081c</t>
+  </si>
+  <si>
+    <t>6e81c28f0eaa1c3e1a5dd84db09b5e6f92be5c80b5af835065b2f344b50fd596</t>
+  </si>
+  <si>
+    <t>af0a78b573f36aac0333ac60d9db0bc337af2149cc5175acc7bcc23cf199ad62</t>
+  </si>
+  <si>
+    <t>8c91402db3756fd051c247cf007a62f897248a5560429063a674a74b710edf1d</t>
+  </si>
+  <si>
+    <t>9cb86cdedf0738bfaa228db74ab108b44b93c94ef045abce219785f1af99aa74</t>
+  </si>
+  <si>
+    <t>0507e8491343d96010ca6f4c0d66fbd6ba3300c3bde055682833f2efe6fb3d7f</t>
+  </si>
+  <si>
+    <t>e888a676e1926d0c08b5f11fb9116df58b62604b05846f39f8d6fc4dd0ba31f1</t>
+  </si>
+  <si>
+    <t>76a23395000b22f2e62a3d76ea317f6f85146298d5cc04dd7c827129eff56fb5</t>
+  </si>
+  <si>
+    <t>a68a5f2e3a4446bfff75a9f9f29d76730a207b273b09c6cb15c314054e46d359</t>
+  </si>
+  <si>
+    <t>26361f9204091993eb1007879841902e560479bc4626da4e582c3a2f1a3ec4c2</t>
+  </si>
+  <si>
+    <t>0b0829e2c11114e877eaaf3115a09f8abe8c3a1bcc9be27925f4df79ce964785</t>
+  </si>
+  <si>
+    <t>aece8aa742ae952451fb745564f60f5f5d6fa6ef09bd4721d6b286be4124eb1f</t>
+  </si>
+  <si>
+    <t>91e631b2fe3d58417b860f962874fbaa2e7471576ee091d9dad2eeb0b92975b8</t>
+  </si>
+  <si>
+    <t>5edbf33e52549fb269123d6eb3e6986bea6c4e03dcbd5223c8591ac25f1a95d4</t>
+  </si>
+  <si>
+    <t>e38e8f8dca36e30898c51bbe4c0956529e51687341386bcb539430281bb955c3</t>
+  </si>
+  <si>
+    <t>ed299bb825b12607dc0fc73ccc777afb0c46ccdd11bbc9a3bfad646f0cdef8fe</t>
+  </si>
+  <si>
+    <t>1ebcb7fc822317c3cdb0c81b047302ddd104a68cefaa8342bb07f881c0735c33</t>
+  </si>
+  <si>
+    <t>6859b2ee8ce053d8c36a1dd51b5a1273f669a89fc2ca3f56d9118c7796c127c6</t>
+  </si>
+  <si>
+    <t>3929469b55e89dd5a16f7037057f8e2b731612da256dc725d30b696fc856c3b7</t>
+  </si>
+  <si>
+    <t>8c96dd3b513429e263faf813625245c5b554ac0de20ff6bdf7b906687ed8ca39</t>
+  </si>
+  <si>
+    <t>7654ca82d2567d5fba3dc2dcbe47664d98da1311a23f80450eb485c41f7082a9</t>
+  </si>
+  <si>
+    <t>35f226b7f4bc034220d2193642e5bae702fca8f34f05e5dd2bb34eb2b3619ee7</t>
+  </si>
+  <si>
+    <t>1ceb7c4da86eab04eee3c5ee7a4b91d740ed0b6b732afddb52aa9fc8a181452b</t>
+  </si>
+  <si>
+    <t>71d8d9487a9d788bc8438b85735d80de37d40faa9749714237ef2c0edc2af288</t>
+  </si>
+  <si>
+    <t>1e27c754e843dd380da596718dc895cf11f0621e2ae9c5b4f5f58ce22bc6097d</t>
+  </si>
+  <si>
+    <t>4ba9f5bafd272a06903c164e043f6d7de16683625387e9fc1e16351f9afc276f</t>
+  </si>
+  <si>
+    <t>7686df94223543a7b4d9fd404590f811e70a76b61972080d88549636c1d8c283</t>
+  </si>
+  <si>
+    <t>4e120bc719a8ee5f9edf3196cbfb3d6c9f039b31acebd667e9bcb089449ee33c</t>
   </si>
 </sst>
 </file>
@@ -362,7 +362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -384,6 +384,7 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -706,7 +707,7 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>22</v>
@@ -714,7 +715,7 @@
     </row>
     <row r="2" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>23</v>
@@ -722,7 +723,7 @@
     </row>
     <row r="3" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>24</v>
@@ -730,7 +731,7 @@
     </row>
     <row r="4" spans="1:2" ht="27.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>25</v>
@@ -738,7 +739,7 @@
     </row>
     <row r="5" spans="1:2" ht="27.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>26</v>
@@ -746,15 +747,15 @@
     </row>
     <row r="6" spans="1:2" ht="27.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="27.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>34</v>
+      <c r="A7" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>28</v>
@@ -775,7 +776,7 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>22</v>
@@ -783,7 +784,7 @@
     </row>
     <row r="2" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>2</v>
@@ -791,7 +792,7 @@
     </row>
     <row r="3" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>13</v>
@@ -799,7 +800,7 @@
     </row>
     <row r="4" spans="1:2" ht="27.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>3</v>
@@ -807,7 +808,7 @@
     </row>
     <row r="5" spans="1:2" ht="27.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>0</v>
@@ -815,7 +816,7 @@
     </row>
     <row r="6" spans="1:2" ht="27.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>1</v>
@@ -823,15 +824,15 @@
     </row>
     <row r="7" spans="1:2" ht="27.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="27.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>41</v>
+      <c r="A8" s="9" t="s">
+        <v>42</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>5</v>
@@ -839,7 +840,7 @@
     </row>
     <row r="9" spans="1:2" ht="27.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>6</v>
@@ -847,7 +848,7 @@
     </row>
     <row r="10" spans="1:2" ht="27.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>14</v>
@@ -855,7 +856,7 @@
     </row>
     <row r="11" spans="1:2" ht="27.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>15</v>
@@ -863,7 +864,7 @@
     </row>
     <row r="12" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>7</v>
@@ -871,7 +872,7 @@
     </row>
     <row r="13" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>8</v>
@@ -879,7 +880,7 @@
     </row>
     <row r="14" spans="1:2" ht="27.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>16</v>
@@ -887,7 +888,7 @@
     </row>
     <row r="15" spans="1:2" ht="27.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>9</v>
@@ -895,7 +896,7 @@
     </row>
     <row r="16" spans="1:2" ht="27.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>17</v>
@@ -903,7 +904,7 @@
     </row>
     <row r="17" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>12</v>
@@ -911,7 +912,7 @@
     </row>
     <row r="18" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>18</v>
@@ -919,7 +920,7 @@
     </row>
     <row r="19" spans="1:2" ht="27.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>19</v>
@@ -927,7 +928,7 @@
     </row>
     <row r="20" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>10</v>
@@ -935,7 +936,7 @@
     </row>
     <row r="21" spans="1:2" ht="40.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>20</v>
@@ -943,7 +944,7 @@
     </row>
     <row r="22" spans="1:2" ht="40.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>21</v>
@@ -951,7 +952,7 @@
     </row>
     <row r="23" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>11</v>

--- a/pass.xlsx
+++ b/pass.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{426B7D7A-21C4-A048-98C8-D998A9D7C601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{86EEAD34-86B3-4466-AB6D-62E57924479D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{86EEAD34-86B3-4466-AB6D-62E57924479D}"/>
   </bookViews>
   <sheets>
     <sheet name="KP" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="80">
   <si>
     <t>Արարատ Արմեն</t>
   </si>
@@ -129,88 +129,88 @@
     <t>pass</t>
   </si>
   <si>
-    <t>7d147b1c41150dc0b4f335a5dec2e37eb876fc3f40106346ed4876de6b38081c</t>
-  </si>
-  <si>
-    <t>6e81c28f0eaa1c3e1a5dd84db09b5e6f92be5c80b5af835065b2f344b50fd596</t>
-  </si>
-  <si>
-    <t>af0a78b573f36aac0333ac60d9db0bc337af2149cc5175acc7bcc23cf199ad62</t>
-  </si>
-  <si>
-    <t>8c91402db3756fd051c247cf007a62f897248a5560429063a674a74b710edf1d</t>
-  </si>
-  <si>
-    <t>9cb86cdedf0738bfaa228db74ab108b44b93c94ef045abce219785f1af99aa74</t>
-  </si>
-  <si>
-    <t>0507e8491343d96010ca6f4c0d66fbd6ba3300c3bde055682833f2efe6fb3d7f</t>
-  </si>
-  <si>
-    <t>e888a676e1926d0c08b5f11fb9116df58b62604b05846f39f8d6fc4dd0ba31f1</t>
-  </si>
-  <si>
-    <t>76a23395000b22f2e62a3d76ea317f6f85146298d5cc04dd7c827129eff56fb5</t>
-  </si>
-  <si>
-    <t>a68a5f2e3a4446bfff75a9f9f29d76730a207b273b09c6cb15c314054e46d359</t>
-  </si>
-  <si>
-    <t>26361f9204091993eb1007879841902e560479bc4626da4e582c3a2f1a3ec4c2</t>
-  </si>
-  <si>
-    <t>0b0829e2c11114e877eaaf3115a09f8abe8c3a1bcc9be27925f4df79ce964785</t>
-  </si>
-  <si>
-    <t>aece8aa742ae952451fb745564f60f5f5d6fa6ef09bd4721d6b286be4124eb1f</t>
-  </si>
-  <si>
-    <t>91e631b2fe3d58417b860f962874fbaa2e7471576ee091d9dad2eeb0b92975b8</t>
-  </si>
-  <si>
-    <t>5edbf33e52549fb269123d6eb3e6986bea6c4e03dcbd5223c8591ac25f1a95d4</t>
-  </si>
-  <si>
-    <t>e38e8f8dca36e30898c51bbe4c0956529e51687341386bcb539430281bb955c3</t>
-  </si>
-  <si>
-    <t>ed299bb825b12607dc0fc73ccc777afb0c46ccdd11bbc9a3bfad646f0cdef8fe</t>
-  </si>
-  <si>
-    <t>1ebcb7fc822317c3cdb0c81b047302ddd104a68cefaa8342bb07f881c0735c33</t>
-  </si>
-  <si>
-    <t>6859b2ee8ce053d8c36a1dd51b5a1273f669a89fc2ca3f56d9118c7796c127c6</t>
-  </si>
-  <si>
-    <t>3929469b55e89dd5a16f7037057f8e2b731612da256dc725d30b696fc856c3b7</t>
-  </si>
-  <si>
-    <t>8c96dd3b513429e263faf813625245c5b554ac0de20ff6bdf7b906687ed8ca39</t>
-  </si>
-  <si>
-    <t>7654ca82d2567d5fba3dc2dcbe47664d98da1311a23f80450eb485c41f7082a9</t>
-  </si>
-  <si>
-    <t>35f226b7f4bc034220d2193642e5bae702fca8f34f05e5dd2bb34eb2b3619ee7</t>
-  </si>
-  <si>
-    <t>1ceb7c4da86eab04eee3c5ee7a4b91d740ed0b6b732afddb52aa9fc8a181452b</t>
-  </si>
-  <si>
-    <t>71d8d9487a9d788bc8438b85735d80de37d40faa9749714237ef2c0edc2af288</t>
-  </si>
-  <si>
-    <t>1e27c754e843dd380da596718dc895cf11f0621e2ae9c5b4f5f58ce22bc6097d</t>
-  </si>
-  <si>
-    <t>4ba9f5bafd272a06903c164e043f6d7de16683625387e9fc1e16351f9afc276f</t>
-  </si>
-  <si>
-    <t>7686df94223543a7b4d9fd404590f811e70a76b61972080d88549636c1d8c283</t>
-  </si>
-  <si>
-    <t>4e120bc719a8ee5f9edf3196cbfb3d6c9f039b31acebd667e9bcb089449ee33c</t>
+    <t>2b0afee33915d17685723c3a4c3d5da99454bd06479c0215c641dee335f84864</t>
+  </si>
+  <si>
+    <t>4cd94bfcc323f48058eb56b8375cd111e33affae8fffebd3fb640e5efa5f8a1e</t>
+  </si>
+  <si>
+    <t>41bc04cc66786185e516bfccdbdec9f51186a5e569ad5baf17bb02e680f38391</t>
+  </si>
+  <si>
+    <t>1ebe243f96149d8793c71432ecaa2618b4e1a5dacd7b9424d07821923147311c</t>
+  </si>
+  <si>
+    <t>9794aff5d0421580705a4be29187ec66569827ed163557d722db79638a927035</t>
+  </si>
+  <si>
+    <t>1a58a653ea150952580c46caf42c4b533a6513c8816d8e182642a88f451af526</t>
+  </si>
+  <si>
+    <t>67c7e180ae3241d6c49204ec0f6d3adbc7849511334c530a01c9e69cb84abb7e</t>
+  </si>
+  <si>
+    <t>0ca842f1cad54272206e0420635c19bd95805b258c01fba635fff693495623f5</t>
+  </si>
+  <si>
+    <t>2da411baf09a35e11d5bea972c62147da834ccac18e96f1a2eed51d3a42cfcf1</t>
+  </si>
+  <si>
+    <t>98d9e56bfb054a422cbcdc2e6fd1509d6b0469992ad617a0a5d92bec60ae0ccf</t>
+  </si>
+  <si>
+    <t>5e9da239584247b76e8a1234d4e07244768bd5d6fe213beac3b2492057ded59a</t>
+  </si>
+  <si>
+    <t>5753680241bffedd1ba54eb849be6424bd62a53ac851f93682b4546424571e70</t>
+  </si>
+  <si>
+    <t>50afe33c3f3f792aa563b9cd2b24d5ef4d6f913db2b5c6e9710199360edb4982</t>
+  </si>
+  <si>
+    <t>6278a76e2d8c305af5a95aeafc0de6a0d6a03b2e2cecbd6c0f0d99fbbfc56c9f</t>
+  </si>
+  <si>
+    <t>887dae4d400a6e01c0400dad8bab61e11b5a5a46b075de60d4a1b0b141d2bb9e</t>
+  </si>
+  <si>
+    <t>aba415659f96505398fcecc86f75f68c739ad7822ba238411e18ae2a0eb08780</t>
+  </si>
+  <si>
+    <t>bcfd5840c32670781a12327e6e840072c768cc19323d05f54c27aa41983f6951</t>
+  </si>
+  <si>
+    <t>52733a3e787bf2687ff7737270cdb7ee0f62d20f363fe5dcf1325c89abf58d23</t>
+  </si>
+  <si>
+    <t>a95523ed24a2db4a53a388e39fdb9afaa58f817a138a7e0c5047ea4e159945ab</t>
+  </si>
+  <si>
+    <t>09f5e68151c0b83031be1d2082e9a0bf8e1055fcbd6b9d7af2389377dae99c03</t>
+  </si>
+  <si>
+    <t>caf800d8acb17733c57871b5aef4900a84ba6bb0ef0d8913d43f70ea037784a6</t>
+  </si>
+  <si>
+    <t>bdf68b31315426c7b8efcce6a848a5a9a06e9aabb087951e07acab8bb7537145</t>
+  </si>
+  <si>
+    <t>a905c1a8eaeb133995f265be212c86b5af7cef3f9d51a6c0352531dc54b96047</t>
+  </si>
+  <si>
+    <t>669bfe60f3bbd21de942421a1e9c5b0c66ad8f2b0fc54e4fc3012f39ec2005e8</t>
+  </si>
+  <si>
+    <t>e5dbab5f260138282f3e53b2dbde03a351bc7b6e1e3a51930a400ca16d7c5d2f</t>
+  </si>
+  <si>
+    <t>a3f82dcb0823b17650bf917a0e0f044e0f4c48cd48105a7f3a07c144bd7c5207</t>
+  </si>
+  <si>
+    <t>e9d022a2fe957beb689d4d89c87ad5a1dde353f1393845767440205c5000ac67</t>
+  </si>
+  <si>
+    <t>e850cde928e60cf121a904758883d1bcd76bdc959fcbbb8ee72cf4b6e79b0c19</t>
   </si>
 </sst>
 </file>
